--- a/PROPERTIES/SUNFLOWER/SUNFLOWER  2025.xlsx
+++ b/PROPERTIES/SUNFLOWER/SUNFLOWER  2025.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="260">
   <si>
     <t xml:space="preserve">SUNFLOWER APARTMENT JAN 30TH STATEMENT 2025</t>
   </si>
@@ -739,12 +739,18 @@
     <t xml:space="preserve">REMARKS</t>
   </si>
   <si>
+    <t xml:space="preserve">METER NUMBERS</t>
+  </si>
+  <si>
     <t xml:space="preserve">BAL/B-FORWAD</t>
   </si>
   <si>
     <t xml:space="preserve">Called on 10/7/25, didn’t pick, twice. Third time picked &amp; said will pay, next week.</t>
   </si>
   <si>
+    <t xml:space="preserve">JEREMY KIRIUNGI</t>
+  </si>
+  <si>
     <t xml:space="preserve">TGA3CBBLBR</t>
   </si>
   <si>
@@ -757,6 +763,12 @@
     <t xml:space="preserve">TG875QFXT9</t>
   </si>
   <si>
+    <t xml:space="preserve">14/7/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGBOKH9Q8K</t>
+  </si>
+  <si>
     <t xml:space="preserve">TG814BMURH</t>
   </si>
   <si>
@@ -764,6 +776,9 @@
   </si>
   <si>
     <t xml:space="preserve">SYLVESTER NZINGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGC1P7GYV3</t>
   </si>
   <si>
     <t xml:space="preserve">TG59S41B1T</t>
@@ -807,7 +822,7 @@
     <numFmt numFmtId="170" formatCode="0"/>
     <numFmt numFmtId="171" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -982,6 +997,19 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="Georgia"/>
@@ -1020,6 +1048,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Georgia"/>
       <family val="1"/>
       <charset val="1"/>
@@ -1122,7 +1156,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="152">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1447,6 +1481,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1471,7 +1509,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1503,7 +1545,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1511,7 +1553,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1527,7 +1569,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1535,19 +1577,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="25" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="27" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1567,19 +1609,19 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1587,11 +1629,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="28" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="30" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1607,7 +1649,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="29" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1627,11 +1669,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="27" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="29" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1639,15 +1681,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="31" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1655,7 +1697,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="29" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1695,7 +1737,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1707,7 +1753,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1715,7 +1761,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7872,7 +7918,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:T43"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="72" width="15.44"/>
@@ -7891,7 +7937,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="72" width="16.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="72" width="39.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="72" width="44.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="72" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="19" min="17" style="72" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="72" width="44.7"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="21" style="72" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7927,746 +7975,827 @@
       <c r="P1" s="80" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="81" t="s">
+      <c r="T1" s="81" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="82"/>
+      <c r="B2" s="83"/>
       <c r="C2" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="83" t="s">
+      <c r="D2" s="84" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="83" t="s">
-        <v>237</v>
-      </c>
-      <c r="F2" s="83" t="s">
+      <c r="E2" s="84" t="s">
+        <v>238</v>
+      </c>
+      <c r="F2" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="83" t="s">
+      <c r="G2" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="84" t="s">
+      <c r="H2" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="84" t="s">
+      <c r="I2" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
       <c r="N2" s="78"/>
-      <c r="O2" s="86"/>
+      <c r="O2" s="87"/>
       <c r="P2" s="72" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="87" t="s">
+        <v>239</v>
+      </c>
+      <c r="T2" s="88"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="88" t="n">
+      <c r="B3" s="85" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3" s="90" t="n">
         <v>790519395</v>
       </c>
-      <c r="D3" s="89" t="n">
+      <c r="D3" s="91" t="n">
         <v>16000</v>
       </c>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="90" t="n">
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="92" t="n">
         <v>16000</v>
       </c>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="92"/>
-      <c r="O3" s="93"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="81" t="s">
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="94"/>
+      <c r="O3" s="95"/>
+      <c r="T3" s="88"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="84"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
-      <c r="N4" s="92"/>
-      <c r="O4" s="93"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="87" t="s">
+      <c r="B4" s="85"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="95"/>
+      <c r="T4" s="88"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="88" t="n">
+      <c r="C5" s="90" t="n">
         <v>726029386</v>
       </c>
-      <c r="D5" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K5" s="91"/>
-      <c r="L5" s="91"/>
-      <c r="M5" s="91"/>
-      <c r="N5" s="94" t="n">
+      <c r="D5" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K5" s="93"/>
+      <c r="L5" s="93"/>
+      <c r="M5" s="93"/>
+      <c r="N5" s="96" t="n">
         <v>45937</v>
       </c>
-      <c r="O5" s="95" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="87" t="s">
+      <c r="O5" s="97" t="s">
+        <v>241</v>
+      </c>
+      <c r="T5" s="88" t="n">
+        <v>54500320103</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="96" t="s">
+      <c r="B6" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="88" t="n">
+      <c r="C6" s="90" t="n">
         <v>743364151</v>
       </c>
-      <c r="D6" s="90" t="n">
+      <c r="D6" s="92" t="n">
         <v>19500</v>
       </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="97"/>
-      <c r="I6" s="90"/>
-      <c r="J6" s="98" t="n">
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="100" t="n">
         <v>19500</v>
       </c>
-      <c r="K6" s="98"/>
-      <c r="L6" s="98"/>
-      <c r="M6" s="98"/>
-      <c r="N6" s="94"/>
-      <c r="O6" s="95"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="87" t="s">
+      <c r="K6" s="100"/>
+      <c r="L6" s="100"/>
+      <c r="M6" s="100"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="97"/>
+      <c r="T6" s="88" t="n">
+        <v>46201831164</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="84" t="s">
-        <v>240</v>
-      </c>
-      <c r="C7" s="99" t="n">
+      <c r="B7" s="85" t="s">
+        <v>242</v>
+      </c>
+      <c r="C7" s="101" t="n">
         <v>708999514</v>
       </c>
-      <c r="D7" s="98" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98" t="n">
-        <v>12000</v>
-      </c>
-      <c r="H7" s="90"/>
-      <c r="I7" s="90"/>
-      <c r="J7" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K7" s="91"/>
-      <c r="L7" s="90"/>
-      <c r="M7" s="90"/>
-      <c r="N7" s="94" t="n">
+      <c r="D7" s="100" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K7" s="93"/>
+      <c r="L7" s="92"/>
+      <c r="M7" s="92"/>
+      <c r="N7" s="96" t="n">
         <v>45784</v>
       </c>
-      <c r="O7" s="95" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="87" t="s">
+      <c r="O7" s="97" t="s">
+        <v>243</v>
+      </c>
+      <c r="T7" s="88" t="n">
+        <v>46201831081</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="85" t="s">
         <v>151</v>
       </c>
-      <c r="C8" s="88" t="n">
+      <c r="C8" s="90" t="n">
         <v>703759351</v>
       </c>
-      <c r="D8" s="90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E8" s="90"/>
-      <c r="F8" s="90"/>
-      <c r="G8" s="90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K8" s="91"/>
-      <c r="L8" s="91"/>
-      <c r="M8" s="91"/>
-      <c r="N8" s="100" t="n">
+      <c r="D8" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H8" s="100"/>
+      <c r="I8" s="100"/>
+      <c r="J8" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K8" s="93"/>
+      <c r="L8" s="93"/>
+      <c r="M8" s="93"/>
+      <c r="N8" s="102" t="n">
         <v>45876</v>
       </c>
-      <c r="O8" s="101" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="81" t="s">
+      <c r="O8" s="103" t="s">
+        <v>244</v>
+      </c>
+      <c r="T8" s="88" t="n">
+        <v>46201831107</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="84"/>
-      <c r="C9" s="88"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="90"/>
-      <c r="J9" s="90"/>
-      <c r="K9" s="91"/>
-      <c r="L9" s="91"/>
-      <c r="M9" s="91"/>
-      <c r="N9" s="102"/>
-      <c r="O9" s="103"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="87" t="s">
+      <c r="B9" s="85"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="93"/>
+      <c r="L9" s="93"/>
+      <c r="M9" s="93"/>
+      <c r="N9" s="104"/>
+      <c r="O9" s="105"/>
+      <c r="T9" s="88"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="85" t="s">
         <v>210</v>
       </c>
-      <c r="C10" s="88" t="n">
+      <c r="C10" s="90" t="n">
         <v>792352751</v>
       </c>
-      <c r="D10" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E10" s="90"/>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="90"/>
-      <c r="J10" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K10" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L10" s="90"/>
-      <c r="M10" s="90"/>
-      <c r="N10" s="104"/>
-      <c r="O10" s="105"/>
-    </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="87" t="s">
+      <c r="D10" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K10" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L10" s="92"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="106"/>
+      <c r="O10" s="107"/>
+      <c r="T10" s="88" t="n">
+        <v>46201831123</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="85" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="88" t="n">
+      <c r="C11" s="90" t="n">
         <v>702668920</v>
       </c>
-      <c r="D11" s="90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E11" s="106"/>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="91"/>
-      <c r="J11" s="90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K11" s="91"/>
-      <c r="L11" s="91"/>
-      <c r="M11" s="91"/>
-      <c r="N11" s="107"/>
-      <c r="O11" s="103"/>
-    </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="87" t="s">
+      <c r="D11" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E11" s="108"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H11" s="92"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K11" s="93"/>
+      <c r="L11" s="93"/>
+      <c r="M11" s="93"/>
+      <c r="N11" s="109" t="s">
+        <v>245</v>
+      </c>
+      <c r="O11" s="105" t="s">
+        <v>246</v>
+      </c>
+      <c r="T11" s="88" t="n">
+        <v>42201808808</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="84" t="s">
+      <c r="B12" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="88" t="n">
+      <c r="C12" s="90" t="n">
         <v>722364736</v>
       </c>
-      <c r="D12" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K12" s="90"/>
-      <c r="L12" s="90"/>
-      <c r="M12" s="90"/>
-      <c r="N12" s="109" t="n">
+      <c r="D12" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H12" s="110"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
+      <c r="M12" s="92"/>
+      <c r="N12" s="111" t="n">
         <v>45876</v>
       </c>
-      <c r="O12" s="105" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="87" t="s">
+      <c r="O12" s="107" t="s">
+        <v>247</v>
+      </c>
+      <c r="T12" s="88" t="n">
+        <v>46201808758</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="84" t="s">
+      <c r="B13" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="110" t="n">
+      <c r="C13" s="112" t="n">
         <v>795080839</v>
       </c>
-      <c r="D13" s="90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E13" s="90"/>
-      <c r="F13" s="90"/>
-      <c r="G13" s="90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="H13" s="90"/>
-      <c r="I13" s="90"/>
-      <c r="J13" s="90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K13" s="91"/>
-      <c r="L13" s="90"/>
-      <c r="M13" s="90"/>
-      <c r="N13" s="107" t="n">
+      <c r="D13" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E13" s="92"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H13" s="92"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K13" s="93"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="109" t="n">
         <v>45937</v>
       </c>
-      <c r="O13" s="111" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="81" t="s">
+      <c r="O13" s="113" t="s">
+        <v>248</v>
+      </c>
+      <c r="T13" s="88" t="n">
+        <v>46201831180</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="84"/>
-      <c r="C14" s="88"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="90"/>
-      <c r="J14" s="90"/>
-      <c r="K14" s="90"/>
-      <c r="L14" s="90"/>
-      <c r="M14" s="90"/>
-      <c r="N14" s="107"/>
-      <c r="O14" s="111"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="87" t="s">
+      <c r="B14" s="85"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="92"/>
+      <c r="F14" s="92"/>
+      <c r="G14" s="92"/>
+      <c r="H14" s="92"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="92"/>
+      <c r="L14" s="92"/>
+      <c r="M14" s="92"/>
+      <c r="N14" s="109"/>
+      <c r="O14" s="113"/>
+      <c r="T14" s="88"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="84" t="s">
+      <c r="B15" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E15" s="90"/>
-      <c r="F15" s="90"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="90"/>
-      <c r="J15" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K15" s="90"/>
-      <c r="L15" s="90"/>
-      <c r="M15" s="90"/>
-      <c r="N15" s="112"/>
-      <c r="O15" s="113"/>
-    </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="114" t="s">
+      <c r="D15" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E15" s="92"/>
+      <c r="F15" s="92"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K15" s="92"/>
+      <c r="L15" s="92"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="114"/>
+      <c r="O15" s="115"/>
+      <c r="T15" s="88" t="n">
+        <v>46201831149</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="116" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="85" t="s">
+        <v>249</v>
+      </c>
+      <c r="C16" s="90" t="n">
+        <v>711447866</v>
+      </c>
+      <c r="D16" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E16" s="92"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H16" s="92"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="117" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K16" s="117"/>
+      <c r="L16" s="117"/>
+      <c r="M16" s="117"/>
+      <c r="N16" s="118" t="s">
         <v>245</v>
       </c>
-      <c r="C16" s="88" t="n">
-        <v>711447866</v>
-      </c>
-      <c r="D16" s="90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E16" s="90"/>
-      <c r="F16" s="90"/>
-      <c r="G16" s="90"/>
-      <c r="H16" s="90"/>
-      <c r="I16" s="90"/>
-      <c r="J16" s="115" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K16" s="115"/>
-      <c r="L16" s="115"/>
-      <c r="M16" s="115"/>
-      <c r="N16" s="116"/>
-      <c r="O16" s="117"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="114" t="s">
+      <c r="O16" s="119" t="s">
+        <v>250</v>
+      </c>
+      <c r="T16" s="88" t="n">
+        <v>46201808782</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="84" t="s">
+      <c r="B17" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="88" t="n">
+      <c r="C17" s="90" t="n">
         <v>746412498</v>
       </c>
-      <c r="D17" s="115" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="90"/>
-      <c r="I17" s="90"/>
-      <c r="J17" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K17" s="118"/>
-      <c r="L17" s="118"/>
-      <c r="M17" s="118"/>
-      <c r="N17" s="119" t="n">
+      <c r="D17" s="117" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E17" s="117"/>
+      <c r="F17" s="117"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="92"/>
+      <c r="I17" s="92"/>
+      <c r="J17" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K17" s="120"/>
+      <c r="L17" s="120"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="121" t="n">
         <v>45876</v>
       </c>
-      <c r="O17" s="105" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="87" t="s">
+      <c r="O17" s="107" t="s">
+        <v>251</v>
+      </c>
+      <c r="T17" s="88" t="n">
+        <v>46201808766</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="84" t="s">
+      <c r="B18" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="120" t="n">
+      <c r="C18" s="122" t="n">
         <v>706281215</v>
       </c>
-      <c r="D18" s="115" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E18" s="115"/>
-      <c r="F18" s="115"/>
-      <c r="G18" s="115"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="115" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K18" s="90"/>
-      <c r="L18" s="90"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="121"/>
-      <c r="O18" s="113"/>
-    </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="81" t="s">
+      <c r="D18" s="117" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K18" s="92"/>
+      <c r="L18" s="92"/>
+      <c r="M18" s="92"/>
+      <c r="N18" s="123"/>
+      <c r="O18" s="115"/>
+      <c r="T18" s="88"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="84"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="90"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="115"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="90"/>
-      <c r="L19" s="90"/>
-      <c r="M19" s="90"/>
-      <c r="N19" s="122"/>
-      <c r="O19" s="113"/>
-    </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="114" t="s">
+      <c r="B19" s="85"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="92"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="117"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="92"/>
+      <c r="M19" s="92"/>
+      <c r="N19" s="124"/>
+      <c r="O19" s="115"/>
+      <c r="T19" s="88"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="116" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="123" t="s">
+      <c r="B20" s="125" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="88" t="n">
+      <c r="C20" s="90" t="n">
         <v>797417523</v>
       </c>
-      <c r="D20" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="H20" s="115"/>
-      <c r="I20" s="115"/>
-      <c r="J20" s="124" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K20" s="124"/>
-      <c r="L20" s="125"/>
-      <c r="M20" s="125"/>
-      <c r="N20" s="126" t="s">
-        <v>247</v>
-      </c>
-      <c r="O20" s="105" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="87" t="s">
+      <c r="D20" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E20" s="92"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H20" s="117"/>
+      <c r="I20" s="117"/>
+      <c r="J20" s="126" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K20" s="126"/>
+      <c r="L20" s="127"/>
+      <c r="M20" s="127"/>
+      <c r="N20" s="128" t="s">
+        <v>252</v>
+      </c>
+      <c r="O20" s="107" t="s">
+        <v>253</v>
+      </c>
+      <c r="T20" s="88" t="n">
+        <v>46201808857</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="84" t="s">
+      <c r="B21" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="127" t="n">
+      <c r="C21" s="129" t="n">
         <v>705299078</v>
       </c>
-      <c r="D21" s="128" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E21" s="128"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="129" t="n">
-        <v>22000</v>
-      </c>
-      <c r="H21" s="90"/>
-      <c r="I21" s="90"/>
-      <c r="J21" s="90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K21" s="90"/>
-      <c r="L21" s="90"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="130" t="n">
+      <c r="D21" s="130" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E21" s="130"/>
+      <c r="F21" s="131"/>
+      <c r="G21" s="131" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H21" s="92"/>
+      <c r="I21" s="92"/>
+      <c r="J21" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K21" s="92"/>
+      <c r="L21" s="92"/>
+      <c r="M21" s="92"/>
+      <c r="N21" s="132" t="n">
         <v>45754</v>
       </c>
-      <c r="O21" s="131" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="87" t="s">
+      <c r="O21" s="133" t="s">
+        <v>254</v>
+      </c>
+      <c r="T21" s="88" t="n">
+        <v>46201808824</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="84" t="s">
+      <c r="B22" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="88" t="n">
+      <c r="C22" s="90" t="n">
         <v>727762079</v>
       </c>
-      <c r="D22" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="98"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="90" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K22" s="90"/>
-      <c r="L22" s="91"/>
-      <c r="M22" s="91"/>
-      <c r="N22" s="132"/>
-      <c r="O22" s="122"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="87" t="s">
+      <c r="D22" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E22" s="92"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="100"/>
+      <c r="I22" s="100"/>
+      <c r="J22" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K22" s="92"/>
+      <c r="L22" s="93"/>
+      <c r="M22" s="93"/>
+      <c r="N22" s="134"/>
+      <c r="O22" s="124"/>
+      <c r="T22" s="88" t="n">
+        <v>46201808790</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="84" t="s">
+      <c r="B23" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="88" t="n">
+      <c r="C23" s="90" t="n">
         <v>755108764</v>
       </c>
-      <c r="D23" s="90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E23" s="90"/>
-      <c r="F23" s="90"/>
-      <c r="G23" s="90"/>
-      <c r="H23" s="90"/>
-      <c r="I23" s="90"/>
-      <c r="J23" s="90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K23" s="91"/>
-      <c r="L23" s="91"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="109"/>
-      <c r="O23" s="93"/>
+      <c r="D23" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K23" s="93"/>
+      <c r="L23" s="93"/>
+      <c r="M23" s="93"/>
+      <c r="N23" s="111"/>
+      <c r="O23" s="95"/>
       <c r="P23" s="72" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="81" t="s">
+        <v>255</v>
+      </c>
+      <c r="T23" s="88" t="n">
+        <v>46201808840</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="84"/>
-      <c r="C24" s="120"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="91"/>
-      <c r="H24" s="91"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="91"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="91"/>
-      <c r="M24" s="91"/>
-      <c r="N24" s="109"/>
-      <c r="O24" s="93"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="87" t="s">
+      <c r="B24" s="85"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="93"/>
+      <c r="M24" s="93"/>
+      <c r="N24" s="111"/>
+      <c r="O24" s="95"/>
+      <c r="T24" s="88"/>
+    </row>
+    <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="89" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="133" t="s">
+      <c r="B25" s="135" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="134"/>
-      <c r="D25" s="135" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E25" s="135"/>
-      <c r="F25" s="136"/>
-      <c r="G25" s="136"/>
-      <c r="H25" s="137"/>
-      <c r="I25" s="136"/>
-      <c r="J25" s="136"/>
-      <c r="K25" s="136"/>
-      <c r="L25" s="136"/>
-      <c r="M25" s="136"/>
-      <c r="N25" s="138"/>
-      <c r="O25" s="139"/>
-    </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="87" t="s">
+      <c r="C25" s="136"/>
+      <c r="D25" s="137" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E25" s="137"/>
+      <c r="F25" s="138"/>
+      <c r="G25" s="138"/>
+      <c r="H25" s="139"/>
+      <c r="I25" s="138"/>
+      <c r="J25" s="138"/>
+      <c r="K25" s="138"/>
+      <c r="L25" s="138"/>
+      <c r="M25" s="138"/>
+      <c r="N25" s="140"/>
+      <c r="O25" s="141"/>
+      <c r="T25" s="88" t="n">
+        <v>46201808865</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="84" t="s">
-        <v>251</v>
-      </c>
-      <c r="C26" s="120" t="n">
+      <c r="B26" s="85" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" s="122" t="n">
         <v>729757926</v>
       </c>
-      <c r="D26" s="90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E26" s="90"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="91"/>
-      <c r="H26" s="91"/>
-      <c r="I26" s="91"/>
-      <c r="J26" s="90" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K26" s="91"/>
-      <c r="L26" s="91"/>
-      <c r="M26" s="91"/>
-      <c r="N26" s="100"/>
-      <c r="O26" s="140"/>
+      <c r="D26" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E26" s="92"/>
+      <c r="F26" s="93"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="93"/>
+      <c r="J26" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K26" s="93"/>
+      <c r="L26" s="93"/>
+      <c r="M26" s="93"/>
+      <c r="N26" s="102"/>
+      <c r="O26" s="142"/>
       <c r="P26" s="72" t="s">
-        <v>252</v>
+        <v>257</v>
+      </c>
+      <c r="T26" s="88" t="n">
+        <v>46201808774</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="88"/>
-      <c r="D27" s="90" t="n">
+      <c r="C27" s="90"/>
+      <c r="D27" s="92" t="n">
         <v>309500</v>
       </c>
-      <c r="E27" s="91"/>
-      <c r="F27" s="91"/>
-      <c r="G27" s="91"/>
-      <c r="H27" s="141" t="n">
+      <c r="E27" s="93"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="93"/>
+      <c r="H27" s="143" t="n">
         <f aca="false">SUM(H3:H26)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="91"/>
-      <c r="J27" s="142"/>
-      <c r="K27" s="142"/>
-      <c r="L27" s="84"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="144"/>
+      <c r="K27" s="144"/>
+      <c r="L27" s="85"/>
       <c r="M27" s="74"/>
       <c r="N27" s="74"/>
-      <c r="O27" s="143"/>
+      <c r="O27" s="145"/>
+      <c r="T27" s="146"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T28" s="81"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T29" s="88"/>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="144"/>
+      <c r="C30" s="147"/>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="72" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="144"/>
+      <c r="C31" s="147"/>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="145"/>
+      <c r="C32" s="148"/>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="146" t="s">
+      <c r="B35" s="149" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="72" t="s">
-        <v>253</v>
-      </c>
-      <c r="C36" s="147"/>
+        <v>258</v>
+      </c>
+      <c r="C36" s="150"/>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="72" t="s">
@@ -8682,7 +8811,7 @@
       <c r="B39" s="72" t="s">
         <v>228</v>
       </c>
-      <c r="D39" s="148"/>
+      <c r="D39" s="151"/>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="72" t="s">
@@ -8693,15 +8822,15 @@
       <c r="B41" s="72" t="s">
         <v>230</v>
       </c>
-      <c r="C41" s="147"/>
+      <c r="C41" s="150"/>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="72" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C43" s="144"/>
+      <c r="C43" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/PROPERTIES/SUNFLOWER/SUNFLOWER  2025.xlsx
+++ b/PROPERTIES/SUNFLOWER/SUNFLOWER  2025.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="265">
   <si>
     <t xml:space="preserve">SUNFLOWER APARTMENT JAN 30TH STATEMENT 2025</t>
   </si>
@@ -751,9 +751,21 @@
     <t xml:space="preserve">JEREMY KIRIUNGI</t>
   </si>
   <si>
+    <t xml:space="preserve">21/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGG18XX4IP</t>
+  </si>
+  <si>
     <t xml:space="preserve">TGA3CBBLBR</t>
   </si>
   <si>
+    <t xml:space="preserve">20/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGK4TL7P9S</t>
+  </si>
+  <si>
     <t xml:space="preserve">SALLY</t>
   </si>
   <si>
@@ -796,7 +808,10 @@
     <t xml:space="preserve">Called on 10/7/25, picked </t>
   </si>
   <si>
-    <t xml:space="preserve">WYCLIFFE </t>
+    <t xml:space="preserve">WICKLIFFE MUTHINI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGJ8NC309W</t>
   </si>
   <si>
     <t xml:space="preserve">Called on 10/7/25, said will pay later.</t>
@@ -822,7 +837,7 @@
     <numFmt numFmtId="170" formatCode="0"/>
     <numFmt numFmtId="171" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1019,6 +1034,14 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <color rgb="FF2E8B57"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <color rgb="FF00A933"/>
       <name val="Georgia"/>
       <family val="1"/>
@@ -1049,6 +1072,13 @@
     <font>
       <sz val="11"/>
       <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
     </font>
@@ -1097,8 +1127,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF81D41A"/>
-        <bgColor rgb="FF969696"/>
+        <fgColor rgb="FF228B22"/>
+        <bgColor rgb="FF2E8B57"/>
       </patternFill>
     </fill>
   </fills>
@@ -1156,7 +1186,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="148">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1537,6 +1567,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1545,7 +1579,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1553,7 +1587,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1569,7 +1603,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1577,19 +1611,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1609,15 +1643,15 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1629,11 +1663,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="30" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="31" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1649,7 +1683,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1669,11 +1703,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="29" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="30" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1681,15 +1715,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="31" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="30" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="32" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="31" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="28" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1697,35 +1731,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="4" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="4" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="4" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1737,11 +1751,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1753,7 +1767,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1761,7 +1775,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1787,11 +1801,11 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF228B22"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
@@ -1820,14 +1834,14 @@
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF81D41A"/>
+      <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF00A933"/>
+      <rgbColor rgb="FF2E8B57"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -8031,17 +8045,25 @@
       </c>
       <c r="E3" s="84"/>
       <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
+      <c r="G3" s="84" t="n">
+        <v>10000</v>
+      </c>
       <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
+      <c r="I3" s="85" t="n">
+        <v>6000</v>
+      </c>
       <c r="J3" s="92" t="n">
         <v>16000</v>
       </c>
       <c r="K3" s="93"/>
       <c r="L3" s="93"/>
       <c r="M3" s="93"/>
-      <c r="N3" s="94"/>
-      <c r="O3" s="95"/>
+      <c r="N3" s="94" t="s">
+        <v>241</v>
+      </c>
+      <c r="O3" s="95" t="s">
+        <v>242</v>
+      </c>
       <c r="T3" s="88"/>
     </row>
     <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8061,7 +8083,7 @@
       <c r="L4" s="93"/>
       <c r="M4" s="93"/>
       <c r="N4" s="94"/>
-      <c r="O4" s="95"/>
+      <c r="O4" s="96"/>
       <c r="T4" s="88"/>
     </row>
     <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8090,11 +8112,11 @@
       <c r="K5" s="93"/>
       <c r="L5" s="93"/>
       <c r="M5" s="93"/>
-      <c r="N5" s="96" t="n">
+      <c r="N5" s="97" t="n">
         <v>45937</v>
       </c>
-      <c r="O5" s="97" t="s">
-        <v>241</v>
+      <c r="O5" s="98" t="s">
+        <v>243</v>
       </c>
       <c r="T5" s="88" t="n">
         <v>54500320103</v>
@@ -8104,7 +8126,7 @@
       <c r="A6" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="98" t="s">
+      <c r="B6" s="99" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="90" t="n">
@@ -8115,17 +8137,23 @@
       </c>
       <c r="E6" s="92"/>
       <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="99"/>
+      <c r="G6" s="92" t="n">
+        <v>19500</v>
+      </c>
+      <c r="H6" s="100"/>
       <c r="I6" s="92"/>
-      <c r="J6" s="100" t="n">
+      <c r="J6" s="101" t="n">
         <v>19500</v>
       </c>
-      <c r="K6" s="100"/>
-      <c r="L6" s="100"/>
-      <c r="M6" s="100"/>
-      <c r="N6" s="96"/>
-      <c r="O6" s="97"/>
+      <c r="K6" s="101"/>
+      <c r="L6" s="101"/>
+      <c r="M6" s="101"/>
+      <c r="N6" s="97" t="s">
+        <v>244</v>
+      </c>
+      <c r="O6" s="98" t="s">
+        <v>245</v>
+      </c>
       <c r="T6" s="88" t="n">
         <v>46201831164</v>
       </c>
@@ -8135,17 +8163,17 @@
         <v>26</v>
       </c>
       <c r="B7" s="85" t="s">
-        <v>242</v>
-      </c>
-      <c r="C7" s="101" t="n">
+        <v>246</v>
+      </c>
+      <c r="C7" s="102" t="n">
         <v>708999514</v>
       </c>
-      <c r="D7" s="100" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="100" t="n">
+      <c r="D7" s="101" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="101" t="n">
         <v>12000</v>
       </c>
       <c r="H7" s="92"/>
@@ -8156,11 +8184,11 @@
       <c r="K7" s="93"/>
       <c r="L7" s="92"/>
       <c r="M7" s="92"/>
-      <c r="N7" s="96" t="n">
+      <c r="N7" s="97" t="n">
         <v>45784</v>
       </c>
-      <c r="O7" s="97" t="s">
-        <v>243</v>
+      <c r="O7" s="98" t="s">
+        <v>247</v>
       </c>
       <c r="T7" s="88" t="n">
         <v>46201831081</v>
@@ -8184,19 +8212,19 @@
       <c r="G8" s="92" t="n">
         <v>22000</v>
       </c>
-      <c r="H8" s="100"/>
-      <c r="I8" s="100"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="101"/>
       <c r="J8" s="92" t="n">
         <v>22000</v>
       </c>
       <c r="K8" s="93"/>
       <c r="L8" s="93"/>
       <c r="M8" s="93"/>
-      <c r="N8" s="102" t="n">
+      <c r="N8" s="103" t="n">
         <v>45876</v>
       </c>
-      <c r="O8" s="103" t="s">
-        <v>244</v>
+      <c r="O8" s="104" t="s">
+        <v>248</v>
       </c>
       <c r="T8" s="88" t="n">
         <v>46201831107</v>
@@ -8218,8 +8246,8 @@
       <c r="K9" s="93"/>
       <c r="L9" s="93"/>
       <c r="M9" s="93"/>
-      <c r="N9" s="104"/>
-      <c r="O9" s="105"/>
+      <c r="N9" s="105"/>
+      <c r="O9" s="106"/>
       <c r="T9" s="88"/>
     </row>
     <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8248,8 +8276,8 @@
       </c>
       <c r="L10" s="92"/>
       <c r="M10" s="92"/>
-      <c r="N10" s="106"/>
-      <c r="O10" s="107"/>
+      <c r="N10" s="107"/>
+      <c r="O10" s="108"/>
       <c r="T10" s="88" t="n">
         <v>46201831123</v>
       </c>
@@ -8267,7 +8295,7 @@
       <c r="D11" s="92" t="n">
         <v>22000</v>
       </c>
-      <c r="E11" s="108"/>
+      <c r="E11" s="109"/>
       <c r="F11" s="92"/>
       <c r="G11" s="92" t="n">
         <v>22000</v>
@@ -8280,11 +8308,11 @@
       <c r="K11" s="93"/>
       <c r="L11" s="93"/>
       <c r="M11" s="93"/>
-      <c r="N11" s="109" t="s">
-        <v>245</v>
-      </c>
-      <c r="O11" s="105" t="s">
-        <v>246</v>
+      <c r="N11" s="110" t="s">
+        <v>249</v>
+      </c>
+      <c r="O11" s="106" t="s">
+        <v>250</v>
       </c>
       <c r="T11" s="88" t="n">
         <v>42201808808</v>
@@ -8308,19 +8336,19 @@
       <c r="G12" s="92" t="n">
         <v>12000</v>
       </c>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
       <c r="J12" s="92" t="n">
         <v>12000</v>
       </c>
       <c r="K12" s="92"/>
       <c r="L12" s="92"/>
       <c r="M12" s="92"/>
-      <c r="N12" s="111" t="n">
+      <c r="N12" s="112" t="n">
         <v>45876</v>
       </c>
-      <c r="O12" s="107" t="s">
-        <v>247</v>
+      <c r="O12" s="108" t="s">
+        <v>251</v>
       </c>
       <c r="T12" s="88" t="n">
         <v>46201808758</v>
@@ -8333,7 +8361,7 @@
       <c r="B13" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="112" t="n">
+      <c r="C13" s="113" t="n">
         <v>795080839</v>
       </c>
       <c r="D13" s="92" t="n">
@@ -8352,11 +8380,11 @@
       <c r="K13" s="93"/>
       <c r="L13" s="92"/>
       <c r="M13" s="92"/>
-      <c r="N13" s="109" t="n">
+      <c r="N13" s="110" t="n">
         <v>45937</v>
       </c>
-      <c r="O13" s="113" t="s">
-        <v>248</v>
+      <c r="O13" s="114" t="s">
+        <v>252</v>
       </c>
       <c r="T13" s="88" t="n">
         <v>46201831180</v>
@@ -8378,8 +8406,8 @@
       <c r="K14" s="92"/>
       <c r="L14" s="92"/>
       <c r="M14" s="92"/>
-      <c r="N14" s="109"/>
-      <c r="O14" s="113"/>
+      <c r="N14" s="110"/>
+      <c r="O14" s="114"/>
       <c r="T14" s="88"/>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8403,18 +8431,18 @@
       <c r="K15" s="92"/>
       <c r="L15" s="92"/>
       <c r="M15" s="92"/>
-      <c r="N15" s="114"/>
-      <c r="O15" s="115"/>
+      <c r="N15" s="115"/>
+      <c r="O15" s="116"/>
       <c r="T15" s="88" t="n">
         <v>46201831149</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="116" t="s">
+      <c r="A16" s="117" t="s">
         <v>50</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C16" s="90" t="n">
         <v>711447866</v>
@@ -8429,24 +8457,24 @@
       </c>
       <c r="H16" s="92"/>
       <c r="I16" s="92"/>
-      <c r="J16" s="117" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K16" s="117"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="117"/>
-      <c r="N16" s="118" t="s">
-        <v>245</v>
-      </c>
-      <c r="O16" s="119" t="s">
-        <v>250</v>
+      <c r="J16" s="118" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K16" s="118"/>
+      <c r="L16" s="118"/>
+      <c r="M16" s="118"/>
+      <c r="N16" s="119" t="s">
+        <v>249</v>
+      </c>
+      <c r="O16" s="120" t="s">
+        <v>254</v>
       </c>
       <c r="T16" s="88" t="n">
         <v>46201808782</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="116" t="s">
+      <c r="A17" s="117" t="s">
         <v>53</v>
       </c>
       <c r="B17" s="85" t="s">
@@ -8455,25 +8483,27 @@
       <c r="C17" s="90" t="n">
         <v>746412498</v>
       </c>
-      <c r="D17" s="117" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
+      <c r="D17" s="118" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="118" t="n">
+        <v>13000</v>
+      </c>
       <c r="H17" s="92"/>
       <c r="I17" s="92"/>
       <c r="J17" s="92" t="n">
         <v>12000</v>
       </c>
-      <c r="K17" s="120"/>
-      <c r="L17" s="120"/>
-      <c r="M17" s="120"/>
-      <c r="N17" s="121" t="n">
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="122" t="n">
         <v>45876</v>
       </c>
-      <c r="O17" s="107" t="s">
-        <v>251</v>
+      <c r="O17" s="108" t="s">
+        <v>255</v>
       </c>
       <c r="T17" s="88" t="n">
         <v>46201808766</v>
@@ -8486,25 +8516,25 @@
       <c r="B18" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="122" t="n">
+      <c r="C18" s="123" t="n">
         <v>706281215</v>
       </c>
-      <c r="D18" s="117" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E18" s="117"/>
-      <c r="F18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117" t="n">
+      <c r="D18" s="118" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="118"/>
+      <c r="I18" s="118"/>
+      <c r="J18" s="118" t="n">
         <v>22000</v>
       </c>
       <c r="K18" s="92"/>
       <c r="L18" s="92"/>
       <c r="M18" s="92"/>
-      <c r="N18" s="123"/>
-      <c r="O18" s="115"/>
+      <c r="N18" s="124"/>
+      <c r="O18" s="116"/>
       <c r="T18" s="88"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8517,21 +8547,21 @@
       <c r="E19" s="92"/>
       <c r="F19" s="92"/>
       <c r="G19" s="92"/>
-      <c r="H19" s="117"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="117"/>
+      <c r="H19" s="118"/>
+      <c r="I19" s="118"/>
+      <c r="J19" s="118"/>
       <c r="K19" s="92"/>
       <c r="L19" s="92"/>
       <c r="M19" s="92"/>
-      <c r="N19" s="124"/>
-      <c r="O19" s="115"/>
+      <c r="N19" s="125"/>
+      <c r="O19" s="116"/>
       <c r="T19" s="88"/>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="116" t="s">
+      <c r="A20" s="117" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="125" t="s">
+      <c r="B20" s="126" t="s">
         <v>61</v>
       </c>
       <c r="C20" s="90" t="n">
@@ -8545,19 +8575,19 @@
       <c r="G20" s="92" t="n">
         <v>12000</v>
       </c>
-      <c r="H20" s="117"/>
-      <c r="I20" s="117"/>
-      <c r="J20" s="126" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K20" s="126"/>
-      <c r="L20" s="127"/>
-      <c r="M20" s="127"/>
-      <c r="N20" s="128" t="s">
-        <v>252</v>
-      </c>
-      <c r="O20" s="107" t="s">
-        <v>253</v>
+      <c r="H20" s="118"/>
+      <c r="I20" s="118"/>
+      <c r="J20" s="127" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K20" s="127"/>
+      <c r="L20" s="128"/>
+      <c r="M20" s="128"/>
+      <c r="N20" s="129" t="s">
+        <v>256</v>
+      </c>
+      <c r="O20" s="108" t="s">
+        <v>257</v>
       </c>
       <c r="T20" s="88" t="n">
         <v>46201808857</v>
@@ -8570,15 +8600,15 @@
       <c r="B21" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="129" t="n">
+      <c r="C21" s="130" t="n">
         <v>705299078</v>
       </c>
-      <c r="D21" s="130" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E21" s="130"/>
-      <c r="F21" s="131"/>
-      <c r="G21" s="131" t="n">
+      <c r="D21" s="131" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E21" s="131"/>
+      <c r="F21" s="132"/>
+      <c r="G21" s="132" t="n">
         <v>22000</v>
       </c>
       <c r="H21" s="92"/>
@@ -8589,11 +8619,11 @@
       <c r="K21" s="92"/>
       <c r="L21" s="92"/>
       <c r="M21" s="92"/>
-      <c r="N21" s="132" t="n">
+      <c r="N21" s="133" t="n">
         <v>45754</v>
       </c>
-      <c r="O21" s="133" t="s">
-        <v>254</v>
+      <c r="O21" s="134" t="s">
+        <v>258</v>
       </c>
       <c r="T21" s="88" t="n">
         <v>46201808824</v>
@@ -8615,16 +8645,16 @@
       <c r="E22" s="92"/>
       <c r="F22" s="92"/>
       <c r="G22" s="92"/>
-      <c r="H22" s="100"/>
-      <c r="I22" s="100"/>
+      <c r="H22" s="101"/>
+      <c r="I22" s="101"/>
       <c r="J22" s="92" t="n">
         <v>12000</v>
       </c>
       <c r="K22" s="92"/>
       <c r="L22" s="93"/>
       <c r="M22" s="93"/>
-      <c r="N22" s="134"/>
-      <c r="O22" s="124"/>
+      <c r="N22" s="135"/>
+      <c r="O22" s="125"/>
       <c r="T22" s="88" t="n">
         <v>46201808790</v>
       </c>
@@ -8653,10 +8683,10 @@
       <c r="K23" s="93"/>
       <c r="L23" s="93"/>
       <c r="M23" s="93"/>
-      <c r="N23" s="111"/>
-      <c r="O23" s="95"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="96"/>
       <c r="P23" s="72" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="T23" s="88" t="n">
         <v>46201808840</v>
@@ -8667,7 +8697,7 @@
         <v>74</v>
       </c>
       <c r="B24" s="85"/>
-      <c r="C24" s="122"/>
+      <c r="C24" s="123"/>
       <c r="D24" s="92"/>
       <c r="E24" s="92"/>
       <c r="F24" s="93"/>
@@ -8678,65 +8708,70 @@
       <c r="K24" s="93"/>
       <c r="L24" s="93"/>
       <c r="M24" s="93"/>
-      <c r="N24" s="111"/>
-      <c r="O24" s="95"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="96"/>
       <c r="T24" s="88"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="89" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="135" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="136"/>
-      <c r="D25" s="137" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E25" s="137"/>
-      <c r="F25" s="138"/>
-      <c r="G25" s="138"/>
-      <c r="H25" s="139"/>
-      <c r="I25" s="138"/>
-      <c r="J25" s="138"/>
-      <c r="K25" s="138"/>
-      <c r="L25" s="138"/>
-      <c r="M25" s="138"/>
-      <c r="N25" s="140"/>
-      <c r="O25" s="141"/>
+      <c r="B25" s="85" t="s">
+        <v>260</v>
+      </c>
+      <c r="C25" s="123" t="n">
+        <v>729757926</v>
+      </c>
+      <c r="D25" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E25" s="92"/>
+      <c r="F25" s="93"/>
+      <c r="G25" s="93" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H25" s="93"/>
+      <c r="I25" s="93"/>
+      <c r="J25" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K25" s="93"/>
+      <c r="L25" s="93"/>
+      <c r="M25" s="93"/>
+      <c r="N25" s="103" t="s">
+        <v>241</v>
+      </c>
+      <c r="O25" s="136" t="s">
+        <v>261</v>
+      </c>
+      <c r="P25" s="72" t="s">
+        <v>262</v>
+      </c>
       <c r="T25" s="88" t="n">
         <v>46201808865</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="85" t="s">
-        <v>256</v>
-      </c>
-      <c r="C26" s="122" t="n">
-        <v>729757926</v>
-      </c>
-      <c r="D26" s="92" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E26" s="92"/>
-      <c r="F26" s="93"/>
-      <c r="G26" s="93"/>
-      <c r="H26" s="93"/>
-      <c r="I26" s="93"/>
-      <c r="J26" s="92" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K26" s="93"/>
-      <c r="L26" s="93"/>
-      <c r="M26" s="93"/>
-      <c r="N26" s="102"/>
-      <c r="O26" s="142"/>
-      <c r="P26" s="72" t="s">
-        <v>257</v>
-      </c>
+      <c r="B26" s="137" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="138"/>
+      <c r="G26" s="138"/>
+      <c r="H26" s="138"/>
+      <c r="I26" s="138"/>
+      <c r="J26" s="138"/>
+      <c r="K26" s="138"/>
+      <c r="L26" s="138"/>
+      <c r="M26" s="138"/>
+      <c r="N26" s="138"/>
+      <c r="O26" s="138"/>
+      <c r="P26" s="138"/>
       <c r="T26" s="88" t="n">
         <v>46201808774</v>
       </c>
@@ -8748,19 +8783,22 @@
       </c>
       <c r="E27" s="93"/>
       <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
-      <c r="H27" s="143" t="n">
+      <c r="G27" s="93" t="n">
+        <f aca="false">SUM(G3:G26)</f>
+        <v>222500</v>
+      </c>
+      <c r="H27" s="139" t="n">
         <f aca="false">SUM(H3:H26)</f>
         <v>0</v>
       </c>
       <c r="I27" s="93"/>
-      <c r="J27" s="144"/>
-      <c r="K27" s="144"/>
+      <c r="J27" s="140"/>
+      <c r="K27" s="140"/>
       <c r="L27" s="85"/>
       <c r="M27" s="74"/>
       <c r="N27" s="74"/>
-      <c r="O27" s="145"/>
-      <c r="T27" s="146"/>
+      <c r="O27" s="141"/>
+      <c r="T27" s="142"/>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="T28" s="81"/>
@@ -8772,30 +8810,30 @@
       <c r="B30" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="147"/>
+      <c r="C30" s="143"/>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="72" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="147"/>
+      <c r="C31" s="143"/>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="148"/>
+      <c r="C32" s="144"/>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="149" t="s">
+      <c r="B35" s="145" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="72" t="s">
-        <v>258</v>
-      </c>
-      <c r="C36" s="150"/>
+        <v>263</v>
+      </c>
+      <c r="C36" s="146"/>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="72" t="s">
@@ -8811,7 +8849,7 @@
       <c r="B39" s="72" t="s">
         <v>228</v>
       </c>
-      <c r="D39" s="151"/>
+      <c r="D39" s="147"/>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="72" t="s">
@@ -8822,15 +8860,15 @@
       <c r="B41" s="72" t="s">
         <v>230</v>
       </c>
-      <c r="C41" s="150"/>
+      <c r="C41" s="146"/>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="72" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C43" s="147"/>
+      <c r="C43" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/PROPERTIES/SUNFLOWER/SUNFLOWER  2025.xlsx
+++ b/PROPERTIES/SUNFLOWER/SUNFLOWER  2025.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="JAN" sheetId="1" state="visible" r:id="rId3"/>
@@ -15,6 +15,7 @@
     <sheet name="MAY" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="JUNE" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="JULY" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="AUG" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="267">
   <si>
     <t xml:space="preserve">SUNFLOWER APARTMENT JAN 30TH STATEMENT 2025</t>
   </si>
@@ -821,6 +822,12 @@
   </si>
   <si>
     <t xml:space="preserve">LABOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/07/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGV4B5S3SO </t>
   </si>
 </sst>
 </file>
@@ -837,7 +844,7 @@
     <numFmt numFmtId="170" formatCode="0"/>
     <numFmt numFmtId="171" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1105,6 +1112,29 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF008000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="15"/>
+      <color rgb="FF008000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1186,7 +1216,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="153">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1776,6 +1806,26 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="37" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1801,11 +1851,11 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF228B22"/>
+      <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF00A933"/>
+      <rgbColor rgb="FF228B22"/>
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
@@ -1822,7 +1872,7 @@
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
@@ -8882,4 +8932,880 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:T43"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="72" width="15.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="72" width="32.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="73" width="24.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="72" width="14.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="72" width="26.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="72" width="17.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="72" width="15.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="72" width="16.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="72" width="14.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="72" width="13.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="72" width="13.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="72" width="16.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="72" width="13.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="72" width="16.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="72" width="39.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="72" width="44.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="19" min="17" style="72" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="72" width="44.7"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="21" style="148" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="74"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="77" t="s">
+        <v>232</v>
+      </c>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="79" t="s">
+        <v>233</v>
+      </c>
+      <c r="K1" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="79" t="s">
+        <v>234</v>
+      </c>
+      <c r="M1" s="79" t="s">
+        <v>235</v>
+      </c>
+      <c r="N1" s="77" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="80" t="s">
+        <v>236</v>
+      </c>
+      <c r="T1" s="81" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="82" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="83"/>
+      <c r="C2" s="76" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="84" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="84" t="s">
+        <v>238</v>
+      </c>
+      <c r="F2" s="84" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="85" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="87"/>
+      <c r="T2" s="88"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="85" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3" s="90" t="n">
+        <v>790519395</v>
+      </c>
+      <c r="D3" s="91" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J3" s="92" t="n">
+        <v>16000</v>
+      </c>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="94"/>
+      <c r="O3" s="95"/>
+      <c r="T3" s="88"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="85"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="96"/>
+      <c r="T4" s="88"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="85" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="90" t="n">
+        <v>726029386</v>
+      </c>
+      <c r="D5" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K5" s="93"/>
+      <c r="L5" s="93"/>
+      <c r="M5" s="93"/>
+      <c r="N5" s="97"/>
+      <c r="O5" s="98"/>
+      <c r="T5" s="88" t="n">
+        <v>54500320103</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="89" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="99" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="90" t="n">
+        <v>743364151</v>
+      </c>
+      <c r="D6" s="92" t="n">
+        <v>19500</v>
+      </c>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="101" t="n">
+        <v>19500</v>
+      </c>
+      <c r="K6" s="101"/>
+      <c r="L6" s="101"/>
+      <c r="M6" s="101"/>
+      <c r="N6" s="97"/>
+      <c r="O6" s="98"/>
+      <c r="T6" s="88" t="n">
+        <v>46201831164</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="89" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="85" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7" s="102" t="n">
+        <v>708999514</v>
+      </c>
+      <c r="D7" s="101" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K7" s="93"/>
+      <c r="L7" s="92"/>
+      <c r="M7" s="92"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="98"/>
+      <c r="T7" s="88" t="n">
+        <v>46201831081</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="89" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="85" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="90" t="n">
+        <v>703759351</v>
+      </c>
+      <c r="D8" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="92"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="101"/>
+      <c r="J8" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K8" s="93"/>
+      <c r="L8" s="93"/>
+      <c r="M8" s="93"/>
+      <c r="N8" s="103"/>
+      <c r="O8" s="104"/>
+      <c r="T8" s="88" t="n">
+        <v>46201831107</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="82" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="85"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="93"/>
+      <c r="L9" s="93"/>
+      <c r="M9" s="93"/>
+      <c r="N9" s="105"/>
+      <c r="O9" s="106"/>
+      <c r="T9" s="88"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="89" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="85" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10" s="90" t="n">
+        <v>792352751</v>
+      </c>
+      <c r="D10" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K10" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L10" s="92"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="107"/>
+      <c r="O10" s="108"/>
+      <c r="T10" s="88" t="n">
+        <v>46201831123</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="89" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="85" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="90" t="n">
+        <v>702668920</v>
+      </c>
+      <c r="D11" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E11" s="109"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K11" s="93"/>
+      <c r="L11" s="93"/>
+      <c r="M11" s="93"/>
+      <c r="N11" s="110"/>
+      <c r="O11" s="106"/>
+      <c r="T11" s="88" t="n">
+        <v>42201808808</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="89" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="85" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="90" t="n">
+        <v>722364736</v>
+      </c>
+      <c r="D12" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
+      <c r="M12" s="92"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="108"/>
+      <c r="T12" s="88" t="n">
+        <v>46201808758</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="89" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="113" t="n">
+        <v>795080839</v>
+      </c>
+      <c r="D13" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E13" s="92"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="92"/>
+      <c r="H13" s="92"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K13" s="93"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="110"/>
+      <c r="O13" s="114"/>
+      <c r="T13" s="88" t="n">
+        <v>46201831180</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="85"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="92"/>
+      <c r="F14" s="92"/>
+      <c r="G14" s="92"/>
+      <c r="H14" s="92"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="92"/>
+      <c r="L14" s="92"/>
+      <c r="M14" s="92"/>
+      <c r="N14" s="110"/>
+      <c r="O14" s="114"/>
+      <c r="T14" s="88"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="89" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E15" s="92"/>
+      <c r="F15" s="92"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K15" s="92"/>
+      <c r="L15" s="92"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="115"/>
+      <c r="O15" s="116"/>
+      <c r="T15" s="88" t="n">
+        <v>46201831149</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="117" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="85" t="s">
+        <v>253</v>
+      </c>
+      <c r="C16" s="90" t="n">
+        <v>711447866</v>
+      </c>
+      <c r="D16" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E16" s="92"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="92"/>
+      <c r="H16" s="92"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="118" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K16" s="118"/>
+      <c r="L16" s="118"/>
+      <c r="M16" s="118"/>
+      <c r="N16" s="119"/>
+      <c r="O16" s="120"/>
+      <c r="T16" s="88" t="n">
+        <v>46201808782</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="117" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="85" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="90" t="n">
+        <v>746412498</v>
+      </c>
+      <c r="D17" s="118" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="92"/>
+      <c r="I17" s="92"/>
+      <c r="J17" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K17" s="121"/>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121"/>
+      <c r="N17" s="122"/>
+      <c r="O17" s="108"/>
+      <c r="T17" s="88" t="n">
+        <v>46201808766</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="89" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="85" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="123" t="n">
+        <v>706281215</v>
+      </c>
+      <c r="D18" s="118" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="118"/>
+      <c r="I18" s="118"/>
+      <c r="J18" s="118" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K18" s="92"/>
+      <c r="L18" s="92"/>
+      <c r="M18" s="92"/>
+      <c r="N18" s="124"/>
+      <c r="O18" s="116"/>
+      <c r="T18" s="88"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="82" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="85"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="92"/>
+      <c r="H19" s="118"/>
+      <c r="I19" s="118"/>
+      <c r="J19" s="118"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="92"/>
+      <c r="M19" s="92"/>
+      <c r="N19" s="125"/>
+      <c r="O19" s="116"/>
+      <c r="T19" s="88"/>
+    </row>
+    <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="117" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="126" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="90" t="n">
+        <v>797417523</v>
+      </c>
+      <c r="D20" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E20" s="92"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="149" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H20" s="118"/>
+      <c r="I20" s="118"/>
+      <c r="J20" s="127" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K20" s="127"/>
+      <c r="L20" s="128"/>
+      <c r="M20" s="128"/>
+      <c r="N20" s="129" t="s">
+        <v>265</v>
+      </c>
+      <c r="O20" s="108" t="s">
+        <v>266</v>
+      </c>
+      <c r="T20" s="88" t="n">
+        <v>46201808857</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="89" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="85" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="130" t="n">
+        <v>705299078</v>
+      </c>
+      <c r="D21" s="131" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E21" s="131"/>
+      <c r="F21" s="132"/>
+      <c r="G21" s="132"/>
+      <c r="H21" s="92"/>
+      <c r="I21" s="92"/>
+      <c r="J21" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K21" s="92"/>
+      <c r="L21" s="92"/>
+      <c r="M21" s="92"/>
+      <c r="N21" s="133"/>
+      <c r="O21" s="134"/>
+      <c r="T21" s="88" t="n">
+        <v>46201808824</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="89" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="90" t="n">
+        <v>727762079</v>
+      </c>
+      <c r="D22" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E22" s="92"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="101"/>
+      <c r="I22" s="101"/>
+      <c r="J22" s="92" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K22" s="92"/>
+      <c r="L22" s="93"/>
+      <c r="M22" s="93"/>
+      <c r="N22" s="135"/>
+      <c r="O22" s="125"/>
+      <c r="T22" s="88" t="n">
+        <v>46201808790</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="89" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="85" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="90" t="n">
+        <v>755108764</v>
+      </c>
+      <c r="D23" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K23" s="93"/>
+      <c r="L23" s="93"/>
+      <c r="M23" s="93"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="96"/>
+      <c r="T23" s="88" t="n">
+        <v>46201808840</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="82" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="85"/>
+      <c r="C24" s="123"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="93"/>
+      <c r="M24" s="93"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="96"/>
+      <c r="T24" s="88"/>
+    </row>
+    <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="89" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="85" t="s">
+        <v>260</v>
+      </c>
+      <c r="C25" s="123" t="n">
+        <v>729757926</v>
+      </c>
+      <c r="D25" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E25" s="92"/>
+      <c r="F25" s="93"/>
+      <c r="G25" s="93"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="93"/>
+      <c r="J25" s="92" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K25" s="93"/>
+      <c r="L25" s="93"/>
+      <c r="M25" s="93"/>
+      <c r="N25" s="103"/>
+      <c r="O25" s="136"/>
+      <c r="T25" s="88" t="n">
+        <v>46201808865</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="89" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="150" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="151"/>
+      <c r="D26" s="151"/>
+      <c r="E26" s="151"/>
+      <c r="F26" s="151"/>
+      <c r="G26" s="151"/>
+      <c r="H26" s="151"/>
+      <c r="I26" s="151"/>
+      <c r="J26" s="151"/>
+      <c r="K26" s="151"/>
+      <c r="L26" s="151"/>
+      <c r="M26" s="151"/>
+      <c r="N26" s="151"/>
+      <c r="O26" s="151"/>
+      <c r="P26" s="151"/>
+      <c r="T26" s="88" t="n">
+        <v>46201808774</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="90"/>
+      <c r="D27" s="92" t="n">
+        <v>309500</v>
+      </c>
+      <c r="E27" s="93"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="152" t="n">
+        <f aca="false">SUM(G3:G26)</f>
+        <v>12000</v>
+      </c>
+      <c r="H27" s="139" t="n">
+        <f aca="false">SUM(H3:H26)</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="93"/>
+      <c r="J27" s="140"/>
+      <c r="K27" s="140"/>
+      <c r="L27" s="85"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="141"/>
+      <c r="T27" s="142"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T28" s="81"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="T29" s="88"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="72" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="143"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="72" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="143"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="144"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="145" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="72" t="s">
+        <v>263</v>
+      </c>
+      <c r="C36" s="146"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="72" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="72" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="72" t="s">
+        <v>228</v>
+      </c>
+      <c r="D39" s="147"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="72" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="72" t="s">
+        <v>230</v>
+      </c>
+      <c r="C41" s="146"/>
+    </row>
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="72" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C43" s="143"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D1:H1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/PROPERTIES/SUNFLOWER/SUNFLOWER  2025.xlsx
+++ b/PROPERTIES/SUNFLOWER/SUNFLOWER  2025.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="270">
   <si>
     <t xml:space="preserve">SUNFLOWER APARTMENT JAN 30TH STATEMENT 2025</t>
   </si>
@@ -824,10 +824,19 @@
     <t xml:space="preserve">LABOR</t>
   </si>
   <si>
+    <t xml:space="preserve">TH54ZUN9WA </t>
+  </si>
+  <si>
     <t xml:space="preserve">31/07/25</t>
   </si>
   <si>
     <t xml:space="preserve">TGV4B5S3SO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH51Z3RWOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WYCLIFFE MUTHINI</t>
   </si>
 </sst>
 </file>
@@ -844,7 +853,7 @@
     <numFmt numFmtId="170" formatCode="0"/>
     <numFmt numFmtId="171" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1121,6 +1130,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF008000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Georgia"/>
@@ -1809,15 +1825,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="37" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1825,7 +1841,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="39" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="40" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8960,7 +8976,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="72" width="44.33"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="19" min="17" style="72" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="72" width="44.7"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="21" style="148" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="21" style="72" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9271,7 +9287,9 @@
       </c>
       <c r="E11" s="109"/>
       <c r="F11" s="92"/>
-      <c r="G11" s="92"/>
+      <c r="G11" s="92" t="n">
+        <v>23000</v>
+      </c>
       <c r="H11" s="92"/>
       <c r="I11" s="93"/>
       <c r="J11" s="92" t="n">
@@ -9280,8 +9298,12 @@
       <c r="K11" s="93"/>
       <c r="L11" s="93"/>
       <c r="M11" s="93"/>
-      <c r="N11" s="110"/>
-      <c r="O11" s="106"/>
+      <c r="N11" s="110" t="n">
+        <v>45785</v>
+      </c>
+      <c r="O11" s="106" t="s">
+        <v>265</v>
+      </c>
       <c r="T11" s="88" t="n">
         <v>42201808808</v>
       </c>
@@ -9516,7 +9538,7 @@
       </c>
       <c r="E20" s="92"/>
       <c r="F20" s="92"/>
-      <c r="G20" s="149" t="n">
+      <c r="G20" s="148" t="n">
         <v>12000</v>
       </c>
       <c r="H20" s="118"/>
@@ -9528,16 +9550,16 @@
       <c r="L20" s="128"/>
       <c r="M20" s="128"/>
       <c r="N20" s="129" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O20" s="108" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="T20" s="88" t="n">
         <v>46201808857</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="89" t="s">
         <v>64</v>
       </c>
@@ -9552,7 +9574,9 @@
       </c>
       <c r="E21" s="131"/>
       <c r="F21" s="132"/>
-      <c r="G21" s="132"/>
+      <c r="G21" s="149" t="n">
+        <v>22000</v>
+      </c>
       <c r="H21" s="92"/>
       <c r="I21" s="92"/>
       <c r="J21" s="92" t="n">
@@ -9561,8 +9585,12 @@
       <c r="K21" s="92"/>
       <c r="L21" s="92"/>
       <c r="M21" s="92"/>
-      <c r="N21" s="133"/>
-      <c r="O21" s="134"/>
+      <c r="N21" s="133" t="n">
+        <v>45785</v>
+      </c>
+      <c r="O21" s="134" t="s">
+        <v>268</v>
+      </c>
       <c r="T21" s="88" t="n">
         <v>46201808824</v>
       </c>
@@ -9652,7 +9680,7 @@
         <v>75</v>
       </c>
       <c r="B25" s="85" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="C25" s="123" t="n">
         <v>729757926</v>
@@ -9711,7 +9739,7 @@
       <c r="F27" s="93"/>
       <c r="G27" s="152" t="n">
         <f aca="false">SUM(G3:G26)</f>
-        <v>12000</v>
+        <v>57000</v>
       </c>
       <c r="H27" s="139" t="n">
         <f aca="false">SUM(H3:H26)</f>

--- a/PROPERTIES/SUNFLOWER/SUNFLOWER  2025.xlsx
+++ b/PROPERTIES/SUNFLOWER/SUNFLOWER  2025.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="272">
   <si>
     <t xml:space="preserve">SUNFLOWER APARTMENT JAN 30TH STATEMENT 2025</t>
   </si>
@@ -837,6 +837,12 @@
   </si>
   <si>
     <t xml:space="preserve">WYCLIFFE MUTHINI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAN WANJIRU KAMAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH648T0SNQ </t>
   </si>
 </sst>
 </file>
@@ -853,7 +859,7 @@
     <numFmt numFmtId="170" formatCode="0"/>
     <numFmt numFmtId="171" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1123,7 +1129,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
+      <sz val="12"/>
       <color rgb="FF008000"/>
       <name val="Georgia"/>
       <family val="1"/>
@@ -1131,13 +1137,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF008000"/>
-      <name val="Georgia"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="16"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Georgia"/>
       <family val="1"/>
@@ -1232,7 +1232,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="166">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1826,22 +1826,74 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="37" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="38" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="39" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="40" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="37" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="37" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="37" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="37" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="37" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8972,7 +9024,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="72" width="16.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="72" width="13.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="72" width="16.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="72" width="39.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="72" width="21.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="72" width="44.33"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="19" min="17" style="72" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="72" width="44.7"/>
@@ -9065,7 +9117,7 @@
       </c>
       <c r="E3" s="84"/>
       <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
+      <c r="G3" s="148"/>
       <c r="H3" s="85"/>
       <c r="I3" s="85" t="n">
         <v>6000</v>
@@ -9077,7 +9129,7 @@
       <c r="L3" s="93"/>
       <c r="M3" s="93"/>
       <c r="N3" s="94"/>
-      <c r="O3" s="95"/>
+      <c r="O3" s="149"/>
       <c r="T3" s="88"/>
     </row>
     <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9089,7 +9141,7 @@
       <c r="D4" s="92"/>
       <c r="E4" s="92"/>
       <c r="F4" s="92"/>
-      <c r="G4" s="92"/>
+      <c r="G4" s="150"/>
       <c r="H4" s="84"/>
       <c r="I4" s="84"/>
       <c r="J4" s="92"/>
@@ -9097,7 +9149,7 @@
       <c r="L4" s="93"/>
       <c r="M4" s="93"/>
       <c r="N4" s="94"/>
-      <c r="O4" s="96"/>
+      <c r="O4" s="149"/>
       <c r="T4" s="88"/>
     </row>
     <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9115,7 +9167,9 @@
       </c>
       <c r="E5" s="92"/>
       <c r="F5" s="92"/>
-      <c r="G5" s="92"/>
+      <c r="G5" s="150" t="n">
+        <v>12000</v>
+      </c>
       <c r="H5" s="84"/>
       <c r="I5" s="84"/>
       <c r="J5" s="92" t="n">
@@ -9125,7 +9179,7 @@
       <c r="L5" s="93"/>
       <c r="M5" s="93"/>
       <c r="N5" s="97"/>
-      <c r="O5" s="98"/>
+      <c r="O5" s="151"/>
       <c r="T5" s="88" t="n">
         <v>54500320103</v>
       </c>
@@ -9145,7 +9199,7 @@
       </c>
       <c r="E6" s="92"/>
       <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
+      <c r="G6" s="150"/>
       <c r="H6" s="100"/>
       <c r="I6" s="92"/>
       <c r="J6" s="101" t="n">
@@ -9155,7 +9209,7 @@
       <c r="L6" s="101"/>
       <c r="M6" s="101"/>
       <c r="N6" s="97"/>
-      <c r="O6" s="98"/>
+      <c r="O6" s="151"/>
       <c r="T6" s="88" t="n">
         <v>46201831164</v>
       </c>
@@ -9175,7 +9229,7 @@
       </c>
       <c r="E7" s="101"/>
       <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
+      <c r="G7" s="152"/>
       <c r="H7" s="92"/>
       <c r="I7" s="92"/>
       <c r="J7" s="92" t="n">
@@ -9185,7 +9239,7 @@
       <c r="L7" s="92"/>
       <c r="M7" s="92"/>
       <c r="N7" s="97"/>
-      <c r="O7" s="98"/>
+      <c r="O7" s="151"/>
       <c r="T7" s="88" t="n">
         <v>46201831081</v>
       </c>
@@ -9205,7 +9259,7 @@
       </c>
       <c r="E8" s="92"/>
       <c r="F8" s="92"/>
-      <c r="G8" s="92"/>
+      <c r="G8" s="150"/>
       <c r="H8" s="101"/>
       <c r="I8" s="101"/>
       <c r="J8" s="92" t="n">
@@ -9215,7 +9269,7 @@
       <c r="L8" s="93"/>
       <c r="M8" s="93"/>
       <c r="N8" s="103"/>
-      <c r="O8" s="104"/>
+      <c r="O8" s="153"/>
       <c r="T8" s="88" t="n">
         <v>46201831107</v>
       </c>
@@ -9229,7 +9283,7 @@
       <c r="D9" s="92"/>
       <c r="E9" s="92"/>
       <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
+      <c r="G9" s="150"/>
       <c r="H9" s="92"/>
       <c r="I9" s="92"/>
       <c r="J9" s="92"/>
@@ -9237,7 +9291,7 @@
       <c r="L9" s="93"/>
       <c r="M9" s="93"/>
       <c r="N9" s="105"/>
-      <c r="O9" s="106"/>
+      <c r="O9" s="154"/>
       <c r="T9" s="88"/>
     </row>
     <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9255,7 +9309,7 @@
       </c>
       <c r="E10" s="92"/>
       <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
+      <c r="G10" s="150"/>
       <c r="H10" s="92"/>
       <c r="I10" s="92"/>
       <c r="J10" s="92" t="n">
@@ -9267,7 +9321,7 @@
       <c r="L10" s="92"/>
       <c r="M10" s="92"/>
       <c r="N10" s="107"/>
-      <c r="O10" s="108"/>
+      <c r="O10" s="149"/>
       <c r="T10" s="88" t="n">
         <v>46201831123</v>
       </c>
@@ -9287,7 +9341,7 @@
       </c>
       <c r="E11" s="109"/>
       <c r="F11" s="92"/>
-      <c r="G11" s="92" t="n">
+      <c r="G11" s="150" t="n">
         <v>23000</v>
       </c>
       <c r="H11" s="92"/>
@@ -9301,7 +9355,7 @@
       <c r="N11" s="110" t="n">
         <v>45785</v>
       </c>
-      <c r="O11" s="106" t="s">
+      <c r="O11" s="154" t="s">
         <v>265</v>
       </c>
       <c r="T11" s="88" t="n">
@@ -9323,7 +9377,7 @@
       </c>
       <c r="E12" s="92"/>
       <c r="F12" s="92"/>
-      <c r="G12" s="92"/>
+      <c r="G12" s="150"/>
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
       <c r="J12" s="92" t="n">
@@ -9333,7 +9387,7 @@
       <c r="L12" s="92"/>
       <c r="M12" s="92"/>
       <c r="N12" s="112"/>
-      <c r="O12" s="108"/>
+      <c r="O12" s="149"/>
       <c r="T12" s="88" t="n">
         <v>46201808758</v>
       </c>
@@ -9353,7 +9407,7 @@
       </c>
       <c r="E13" s="92"/>
       <c r="F13" s="92"/>
-      <c r="G13" s="92"/>
+      <c r="G13" s="150"/>
       <c r="H13" s="92"/>
       <c r="I13" s="92"/>
       <c r="J13" s="92" t="n">
@@ -9363,7 +9417,7 @@
       <c r="L13" s="92"/>
       <c r="M13" s="92"/>
       <c r="N13" s="110"/>
-      <c r="O13" s="114"/>
+      <c r="O13" s="155"/>
       <c r="T13" s="88" t="n">
         <v>46201831180</v>
       </c>
@@ -9377,7 +9431,7 @@
       <c r="D14" s="92"/>
       <c r="E14" s="92"/>
       <c r="F14" s="92"/>
-      <c r="G14" s="92"/>
+      <c r="G14" s="150"/>
       <c r="H14" s="92"/>
       <c r="I14" s="92"/>
       <c r="J14" s="92"/>
@@ -9385,7 +9439,7 @@
       <c r="L14" s="92"/>
       <c r="M14" s="92"/>
       <c r="N14" s="110"/>
-      <c r="O14" s="114"/>
+      <c r="O14" s="155"/>
       <c r="T14" s="88"/>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9400,7 +9454,7 @@
       </c>
       <c r="E15" s="92"/>
       <c r="F15" s="92"/>
-      <c r="G15" s="92"/>
+      <c r="G15" s="150"/>
       <c r="H15" s="92"/>
       <c r="I15" s="92"/>
       <c r="J15" s="92" t="n">
@@ -9410,7 +9464,7 @@
       <c r="L15" s="92"/>
       <c r="M15" s="92"/>
       <c r="N15" s="115"/>
-      <c r="O15" s="116"/>
+      <c r="O15" s="156"/>
       <c r="T15" s="88" t="n">
         <v>46201831149</v>
       </c>
@@ -9430,7 +9484,7 @@
       </c>
       <c r="E16" s="92"/>
       <c r="F16" s="92"/>
-      <c r="G16" s="92"/>
+      <c r="G16" s="150"/>
       <c r="H16" s="92"/>
       <c r="I16" s="92"/>
       <c r="J16" s="118" t="n">
@@ -9440,7 +9494,7 @@
       <c r="L16" s="118"/>
       <c r="M16" s="118"/>
       <c r="N16" s="119"/>
-      <c r="O16" s="120"/>
+      <c r="O16" s="157"/>
       <c r="T16" s="88" t="n">
         <v>46201808782</v>
       </c>
@@ -9460,7 +9514,9 @@
       </c>
       <c r="E17" s="118"/>
       <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
+      <c r="G17" s="158" t="n">
+        <v>13000</v>
+      </c>
       <c r="H17" s="92"/>
       <c r="I17" s="92"/>
       <c r="J17" s="92" t="n">
@@ -9470,7 +9526,7 @@
       <c r="L17" s="121"/>
       <c r="M17" s="121"/>
       <c r="N17" s="122"/>
-      <c r="O17" s="108"/>
+      <c r="O17" s="149"/>
       <c r="T17" s="88" t="n">
         <v>46201808766</v>
       </c>
@@ -9490,7 +9546,7 @@
       </c>
       <c r="E18" s="118"/>
       <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
+      <c r="G18" s="158"/>
       <c r="H18" s="118"/>
       <c r="I18" s="118"/>
       <c r="J18" s="118" t="n">
@@ -9500,7 +9556,7 @@
       <c r="L18" s="92"/>
       <c r="M18" s="92"/>
       <c r="N18" s="124"/>
-      <c r="O18" s="116"/>
+      <c r="O18" s="156"/>
       <c r="T18" s="88"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9512,7 +9568,7 @@
       <c r="D19" s="92"/>
       <c r="E19" s="92"/>
       <c r="F19" s="92"/>
-      <c r="G19" s="92"/>
+      <c r="G19" s="150"/>
       <c r="H19" s="118"/>
       <c r="I19" s="118"/>
       <c r="J19" s="118"/>
@@ -9520,10 +9576,10 @@
       <c r="L19" s="92"/>
       <c r="M19" s="92"/>
       <c r="N19" s="125"/>
-      <c r="O19" s="116"/>
+      <c r="O19" s="156"/>
       <c r="T19" s="88"/>
     </row>
-    <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="117" t="s">
         <v>60</v>
       </c>
@@ -9538,7 +9594,7 @@
       </c>
       <c r="E20" s="92"/>
       <c r="F20" s="92"/>
-      <c r="G20" s="148" t="n">
+      <c r="G20" s="150" t="n">
         <v>12000</v>
       </c>
       <c r="H20" s="118"/>
@@ -9552,14 +9608,14 @@
       <c r="N20" s="129" t="s">
         <v>266</v>
       </c>
-      <c r="O20" s="108" t="s">
+      <c r="O20" s="149" t="s">
         <v>267</v>
       </c>
       <c r="T20" s="88" t="n">
         <v>46201808857</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="89" t="s">
         <v>64</v>
       </c>
@@ -9574,7 +9630,7 @@
       </c>
       <c r="E21" s="131"/>
       <c r="F21" s="132"/>
-      <c r="G21" s="149" t="n">
+      <c r="G21" s="159" t="n">
         <v>22000</v>
       </c>
       <c r="H21" s="92"/>
@@ -9588,7 +9644,7 @@
       <c r="N21" s="133" t="n">
         <v>45785</v>
       </c>
-      <c r="O21" s="134" t="s">
+      <c r="O21" s="160" t="s">
         <v>268</v>
       </c>
       <c r="T21" s="88" t="n">
@@ -9620,7 +9676,7 @@
       <c r="L22" s="93"/>
       <c r="M22" s="93"/>
       <c r="N22" s="135"/>
-      <c r="O22" s="125"/>
+      <c r="O22" s="154"/>
       <c r="T22" s="88" t="n">
         <v>46201808790</v>
       </c>
@@ -9650,7 +9706,7 @@
       <c r="L23" s="93"/>
       <c r="M23" s="93"/>
       <c r="N23" s="112"/>
-      <c r="O23" s="96"/>
+      <c r="O23" s="149"/>
       <c r="T23" s="88" t="n">
         <v>46201808840</v>
       </c>
@@ -9672,7 +9728,7 @@
       <c r="L24" s="93"/>
       <c r="M24" s="93"/>
       <c r="N24" s="112"/>
-      <c r="O24" s="96"/>
+      <c r="O24" s="149"/>
       <c r="T24" s="88"/>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9700,32 +9756,36 @@
       <c r="L25" s="93"/>
       <c r="M25" s="93"/>
       <c r="N25" s="103"/>
-      <c r="O25" s="136"/>
+      <c r="O25" s="161"/>
       <c r="T25" s="88" t="n">
         <v>46201808865</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="150" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="151"/>
-      <c r="D26" s="151"/>
-      <c r="E26" s="151"/>
-      <c r="F26" s="151"/>
-      <c r="G26" s="151"/>
-      <c r="H26" s="151"/>
-      <c r="I26" s="151"/>
-      <c r="J26" s="151"/>
-      <c r="K26" s="151"/>
-      <c r="L26" s="151"/>
-      <c r="M26" s="151"/>
-      <c r="N26" s="151"/>
-      <c r="O26" s="151"/>
-      <c r="P26" s="151"/>
+      <c r="B26" s="162" t="s">
+        <v>270</v>
+      </c>
+      <c r="C26" s="163"/>
+      <c r="D26" s="163"/>
+      <c r="E26" s="163"/>
+      <c r="F26" s="163"/>
+      <c r="G26" s="163"/>
+      <c r="H26" s="163"/>
+      <c r="I26" s="163"/>
+      <c r="J26" s="163"/>
+      <c r="K26" s="163" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L26" s="163"/>
+      <c r="M26" s="163"/>
+      <c r="N26" s="163"/>
+      <c r="O26" s="164" t="s">
+        <v>271</v>
+      </c>
+      <c r="P26" s="163"/>
       <c r="T26" s="88" t="n">
         <v>46201808774</v>
       </c>
@@ -9737,9 +9797,9 @@
       </c>
       <c r="E27" s="93"/>
       <c r="F27" s="93"/>
-      <c r="G27" s="152" t="n">
+      <c r="G27" s="165" t="n">
         <f aca="false">SUM(G3:G26)</f>
-        <v>57000</v>
+        <v>82000</v>
       </c>
       <c r="H27" s="139" t="n">
         <f aca="false">SUM(H3:H26)</f>

--- a/PROPERTIES/SUNFLOWER/SUNFLOWER  2025.xlsx
+++ b/PROPERTIES/SUNFLOWER/SUNFLOWER  2025.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="274">
   <si>
     <t xml:space="preserve">SUNFLOWER APARTMENT JAN 30TH STATEMENT 2025</t>
   </si>
@@ -822,6 +822,12 @@
   </si>
   <si>
     <t xml:space="preserve">LABOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/08/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE69JKL84 </t>
   </si>
   <si>
     <t xml:space="preserve">TH54ZUN9WA </t>
@@ -1232,7 +1238,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="164">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1883,14 +1889,6 @@
     </xf>
     <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="39" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -9309,7 +9307,9 @@
       </c>
       <c r="E10" s="92"/>
       <c r="F10" s="92"/>
-      <c r="G10" s="150"/>
+      <c r="G10" s="150" t="n">
+        <v>12000</v>
+      </c>
       <c r="H10" s="92"/>
       <c r="I10" s="92"/>
       <c r="J10" s="92" t="n">
@@ -9320,8 +9320,12 @@
       </c>
       <c r="L10" s="92"/>
       <c r="M10" s="92"/>
-      <c r="N10" s="107"/>
-      <c r="O10" s="149"/>
+      <c r="N10" s="107" t="s">
+        <v>265</v>
+      </c>
+      <c r="O10" s="149" t="s">
+        <v>266</v>
+      </c>
       <c r="T10" s="88" t="n">
         <v>46201831123</v>
       </c>
@@ -9356,7 +9360,7 @@
         <v>45785</v>
       </c>
       <c r="O11" s="154" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="T11" s="88" t="n">
         <v>42201808808</v>
@@ -9606,10 +9610,10 @@
       <c r="L20" s="128"/>
       <c r="M20" s="128"/>
       <c r="N20" s="129" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O20" s="149" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="T20" s="88" t="n">
         <v>46201808857</v>
@@ -9645,7 +9649,7 @@
         <v>45785</v>
       </c>
       <c r="O21" s="160" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="T21" s="88" t="n">
         <v>46201808824</v>
@@ -9736,7 +9740,7 @@
         <v>75</v>
       </c>
       <c r="B25" s="85" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C25" s="123" t="n">
         <v>729757926</v>
@@ -9761,31 +9765,19 @@
         <v>46201808865</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" s="72" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="89" t="s">
         <v>77</v>
       </c>
       <c r="B26" s="162" t="s">
-        <v>270</v>
-      </c>
-      <c r="C26" s="163"/>
-      <c r="D26" s="163"/>
-      <c r="E26" s="163"/>
-      <c r="F26" s="163"/>
-      <c r="G26" s="163"/>
-      <c r="H26" s="163"/>
-      <c r="I26" s="163"/>
-      <c r="J26" s="163"/>
-      <c r="K26" s="163" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L26" s="163"/>
-      <c r="M26" s="163"/>
-      <c r="N26" s="163"/>
-      <c r="O26" s="164" t="s">
-        <v>271</v>
-      </c>
-      <c r="P26" s="163"/>
+        <v>272</v>
+      </c>
+      <c r="K26" s="72" t="n">
+        <v>12000</v>
+      </c>
+      <c r="O26" s="151" t="s">
+        <v>273</v>
+      </c>
       <c r="T26" s="88" t="n">
         <v>46201808774</v>
       </c>
@@ -9797,9 +9789,9 @@
       </c>
       <c r="E27" s="93"/>
       <c r="F27" s="93"/>
-      <c r="G27" s="165" t="n">
+      <c r="G27" s="163" t="n">
         <f aca="false">SUM(G3:G26)</f>
-        <v>82000</v>
+        <v>94000</v>
       </c>
       <c r="H27" s="139" t="n">
         <f aca="false">SUM(H3:H26)</f>
